--- a/output/Data and Chart Outputs/bolivia_gas_demand_by_sector.xlsx
+++ b/output/Data and Chart Outputs/bolivia_gas_demand_by_sector.xlsx
@@ -23,8 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,9 +65,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -330,7 +332,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr/>
           </a:p>
@@ -368,6 +370,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -556,7 +564,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr/>
           </a:p>
@@ -594,6 +602,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -713,7 +727,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr/>
           </a:p>
@@ -751,6 +765,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1327,7 +1347,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1347,7 +1367,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1367,7 +1387,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1387,7 +1407,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1407,7 +1427,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1427,7 +1447,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1447,7 +1467,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1467,7 +1487,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1487,7 +1507,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1507,7 +1527,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1527,7 +1547,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1547,7 +1567,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1567,7 +1587,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1587,7 +1607,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1607,7 +1627,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1627,7 +1647,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1647,7 +1667,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1667,7 +1687,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1687,7 +1707,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1707,7 +1727,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1727,7 +1747,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1747,7 +1767,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1767,7 +1787,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1787,7 +1807,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1807,7 +1827,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1827,7 +1847,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1847,7 +1867,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1867,7 +1887,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1887,7 +1907,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1907,7 +1927,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1927,7 +1947,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1947,7 +1967,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1967,7 +1987,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1987,7 +2007,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -2007,7 +2027,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2027,7 +2047,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2047,7 +2067,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2067,7 +2087,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2087,7 +2107,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2107,7 +2127,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2127,7 +2147,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2147,7 +2167,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2167,7 +2187,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2187,7 +2207,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2207,7 +2227,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2227,7 +2247,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2247,7 +2267,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2267,7 +2287,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2287,7 +2307,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2307,7 +2327,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2327,7 +2347,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2347,7 +2367,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2367,7 +2387,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2387,7 +2407,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2407,7 +2427,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2427,7 +2447,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2447,7 +2467,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2467,7 +2487,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2487,7 +2507,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2507,7 +2527,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2572,7 +2592,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -2589,7 +2609,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -2606,7 +2626,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -2623,7 +2643,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -2640,7 +2660,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -2657,7 +2677,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -2674,7 +2694,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -2691,7 +2711,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -2708,7 +2728,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -2725,7 +2745,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -2742,7 +2762,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -2759,7 +2779,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -2776,7 +2796,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -2793,7 +2813,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -2810,7 +2830,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -2827,7 +2847,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -2844,7 +2864,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -2861,7 +2881,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -2878,7 +2898,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -2895,7 +2915,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -2912,7 +2932,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -2929,7 +2949,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -2946,7 +2966,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -2963,7 +2983,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -2980,7 +3000,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -2997,7 +3017,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -3014,7 +3034,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -3031,7 +3051,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -3048,7 +3068,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -3065,7 +3085,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -3082,7 +3102,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -3099,7 +3119,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -3116,7 +3136,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -3133,7 +3153,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -3150,7 +3170,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -3167,7 +3187,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -3184,7 +3204,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -3201,7 +3221,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -3218,7 +3238,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -3235,7 +3255,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -3252,7 +3272,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -3269,7 +3289,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -3286,7 +3306,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -3303,7 +3323,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -3320,7 +3340,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -3337,7 +3357,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -3354,7 +3374,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -3371,7 +3391,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -3388,7 +3408,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -3405,7 +3425,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -3422,7 +3442,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -3439,7 +3459,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -3456,7 +3476,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -3473,7 +3493,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -3490,7 +3510,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -3507,7 +3527,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -3524,7 +3544,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -3541,7 +3561,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -3558,7 +3578,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -3575,7 +3595,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -3627,7 +3647,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -3638,7 +3658,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -3649,7 +3669,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -3660,7 +3680,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -3671,7 +3691,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -3682,7 +3702,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -3693,7 +3713,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -3704,7 +3724,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -3715,7 +3735,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -3726,7 +3746,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -3737,7 +3757,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -3748,7 +3768,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -3759,7 +3779,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -3770,7 +3790,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -3781,7 +3801,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -3792,7 +3812,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -3803,7 +3823,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -3814,7 +3834,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -3825,7 +3845,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -3836,7 +3856,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -3847,7 +3867,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -3858,7 +3878,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -3869,7 +3889,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -3880,7 +3900,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -3891,7 +3911,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -3902,7 +3922,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -3913,7 +3933,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -3924,7 +3944,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -3935,7 +3955,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -3946,7 +3966,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -3957,7 +3977,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -3968,7 +3988,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -3979,7 +3999,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -3990,7 +4010,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -4001,7 +4021,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -4012,7 +4032,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -4023,7 +4043,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -4034,7 +4054,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -4045,7 +4065,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -4056,7 +4076,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -4067,7 +4087,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -4078,7 +4098,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -4089,7 +4109,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -4100,7 +4120,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -4111,7 +4131,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -4122,7 +4142,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -4133,7 +4153,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -4144,7 +4164,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -4155,7 +4175,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -4166,7 +4186,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -4177,7 +4197,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -4188,7 +4208,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -4199,7 +4219,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -4210,7 +4230,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -4221,7 +4241,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -4232,7 +4252,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -4243,7 +4263,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -4254,7 +4274,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -4265,7 +4285,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -4276,7 +4296,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -4287,7 +4307,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -4298,7 +4318,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -4309,7 +4329,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -4320,7 +4340,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -4331,7 +4351,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -4342,7 +4362,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -4353,7 +4373,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -4364,7 +4384,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">

--- a/output/Data and Chart Outputs/bolivia_gas_demand_by_sector.xlsx
+++ b/output/Data and Chart Outputs/bolivia_gas_demand_by_sector.xlsx
@@ -158,6 +158,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Bolivia gas demand by sector (to Dec/25)</a:t>
             </a:r>
           </a:p>
@@ -405,6 +406,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Bolivia gas production vs exports + domestic demand (to Dec/25)</a:t>
             </a:r>
           </a:p>
@@ -637,6 +639,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Bolivia gas exports by destination (INE customs) (to Aug/26)</a:t>
             </a:r>
           </a:p>
